--- a/output/graficos_dimensiones/comunal_p_basica_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:42</t>
+    <t xml:space="preserve">2026-09-09 23:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:41</t>
+    <t xml:space="preserve">2026-09-18 10:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:30</t>
+    <t xml:space="preserve">2026-09-23 13:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:02</t>
+    <t xml:space="preserve">2026-10-02 15:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2020_biobio.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Laja</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Negrete</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:13</t>
+    <t xml:space="preserve">2026-10-04 09:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:47</t>
+    <t xml:space="preserve">2026-10-05 13:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
